--- a/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 스미스 선생입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 비행이 저한테 너무 무서운 일이 돼서 왔어요. 비행기를 탄다는 생각만 해도 정말 심하게 겁이 나요. 말이 안 된다는 걸 알긴 하는데, 제 몸은 그 비행기가 떨어질 거라고 확신하고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 비행이나 비행기와 전혀 상관없는 상황에서도 이런 강렬한 두려움이나 공황 삽화가 느닷없이 찾아오는 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 느닷없이 그런 게 생기는 건 못 느꼈어요. 정말로 비행이나 그 생각 자체와 연결돼 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 비행 말고도, 사람 많은 곳이나 엘리베이터 같은 밀폐된 공간, 집에서 멀리 떨어지는 상황처럼 다른 상황에서도 강렬한 두려움을 느끼거나 그런 상황을 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 다른 상황에서는 딱히 그런 걸 못 느꼈어요. 주로 비행기와 비행이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 배제됨: 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 특정공포증 (D012)
 인구통계: 성별 남성 / 나이 40 / 직업상태 physician / 최종학력 중학교 중퇴 이하
@@ -575,131 +642,32 @@
 증상 지속 기간: 7 months
 추가 요건: 
 주호소 증상 코드: S062
-배경 서술: 에스테반은 행정 구조조정 과정에서 지역사회 진료소에서 해고된 후, 캘리포니아 전역의 시골 진료소로 경비행기를 타고 이동해야 하는 단기 대체 진료 자리를 수락했다. 첫 비행에서 겪은 심한 난기류로 인해 비행이 위협적인 것으로 각인되었고, 이후 7개월 동안 비행기에 대한 그의 두려움은 즉각적이고 과도한 것이 되어 진료 근무를 취소하고, 학회 참석을 피하고, 오래전부터 계획했던 온두라스의 가족 방문까지 미루게 만들었다. 항공 이동이 그의 수입과 직업적 평판, 가족에 대한 의무와 직결되어 있었기 때문에 이 회피는 상당한 기능 저하를 일으켰고, 그가 가치 있게 여기던 일까지 거절하게 만들었다. 이 두려움이 자신의 의료 활동과 개인적인 삶을 모두 좁혀놓았다는 것을 깨달은 그는 의사 건강 네트워크를 통해 스스로 정신과에 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요—저는 스미스 선생입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 비행이 저한테 너무 무서운 일이 돼서 왔어요. 비행기를 탄다는 생각만 해도 정말 심하게 겁이 나요. 말이 안 된다는 걸 알긴 하는데, 제 몸은 그 비행기가 떨어질 거라고 확신하고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 비행이나 비행기와 전혀 상관없는 상황에서도 이런 강렬한 두려움이나 공황 삽화가 느닷없이 찾아오는 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 느닷없이 그런 게 생기는 건 못 느꼈어요. 정말로 비행이나 그 생각 자체와 연결돼 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 비행 말고도, 사람 많은 곳이나 엘리베이터 같은 밀폐된 공간, 집에서 멀리 떨어지는 상황처럼 다른 상황에서도 강렬한 두려움을 느끼거나 그런 상황을 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 다른 상황에서는 딱히 그런 걸 못 느꼈어요. 주로 비행기와 비행이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 에스테반은 행정 구조조정 과정에서 지역사회 진료소에서 해고된 후, 캘리포니아 전역의 시골 진료소로 경비행기를 타고 이동해야 하는 단기 대체 진료 자리를 수락했다. 첫 비행에서 겪은 심한 난기류로 인해 비행이 위협적인 것으로 각인되었고, 이후 7개월 동안 비행기에 대한 그의 두려움은 즉각적이고 과도한 것이 되어 진료 근무를 취소하고, 학회 참석을 피하고, 오래전부터 계획했던 온두라스의 가족 방문까지 미루게 만들었다. 항공 이동이 그의 수입과 직업적 평판, 가족에 대한 의무와 직결되어 있었기 때문에 이 회피는 상당한 기능 저하를 일으켰고, 그가 가치 있게 여기던 일까지 거절하게 만들었다. 이 두려움이 자신의 의료 활동과 개인적인 삶을 모두 좁혀놓았다는 것을 깨달은 그는 의사 건강 네트워크를 통해 스스로 정신과에 의뢰했다.
+표집된 증상 목록:
+  - S062 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - S063 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
+  - S064 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 배제됨: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
-  확인된 근거: 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).; 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
-  누락: 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)
+지속 기간 요건: 없음
+기능적 손상 요건: 없음
+추가 요건: None
+체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
+확인된 근거:
+  - 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -663,11 +668,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S001_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
